--- a/data/信用债发行汇总_2026-08-14.xlsx
+++ b/data/信用债发行汇总_2026-08-14.xlsx
@@ -745,11 +745,19 @@
           <t>四川省-成都市</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>26成都开投PPN001</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>4.94Y+5.00Y</t>
+        </is>
+      </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.1775</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -1346,11 +1354,19 @@
           <t>四川省-成都市</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>26成都开投PPN001</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>4.94Y+5.00Y</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.1775</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
